--- a/ZZ- paper/ZZ_ZYG11B_ZER1_hit_lists.xlsx
+++ b/ZZ- paper/ZZ_ZYG11B_ZER1_hit_lists.xlsx
@@ -16603,7 +16603,7 @@
       </c>
       <c r="B187" t="inlineStr">
         <is>
-          <t>2004-09-01 00:00:00</t>
+          <t>SEPTIN4</t>
         </is>
       </c>
       <c r="C187" t="inlineStr">
@@ -22086,7 +22086,7 @@
       </c>
       <c r="B81" t="inlineStr">
         <is>
-          <t>2004-09-01 00:00:00</t>
+          <t>SEPTIN4</t>
         </is>
       </c>
       <c r="C81" t="inlineStr">
@@ -30236,7 +30236,7 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="10" customWidth="1" min="1" max="1"/>
-    <col width="21" customWidth="1" min="2" max="2"/>
+    <col width="13" customWidth="1" min="2" max="2"/>
     <col width="20" customWidth="1" min="3" max="3"/>
     <col width="43" customWidth="1" min="4" max="4"/>
     <col width="14" customWidth="1" min="5" max="5"/>
@@ -33573,7 +33573,7 @@
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>2004-09-01 00:00:00</t>
+          <t>SEPTIN4</t>
         </is>
       </c>
       <c r="C57" t="inlineStr">
